--- a/data/2.full_abstracting/26_01_06_fullabstracting.xlsx
+++ b/data/2.full_abstracting/26_01_06_fullabstracting.xlsx
@@ -1,158 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AC77FDCE8F79A8D366075C52F3B7F273C06D9C7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05273176-0B9B-480B-8776-31E2A75F79D2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>doi</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>journal</t>
-  </si>
-  <si>
-    <t>authors</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>abstract</t>
-  </si>
-  <si>
-    <t>decision</t>
-  </si>
-  <si>
-    <t>rayyan-409799136</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>10.1016/j.tate.2025.105340</t>
-  </si>
-  <si>
-    <t>TEACHING AND TEACHER EDUCATION</t>
-  </si>
-  <si>
-    <t>Yuste-Hidalgo, Francisco and Stefanelli, Federica and Menesini, Ersilia and Llorent, Vicente J.</t>
-  </si>
-  <si>
-    <t>Longitudinal association between teachers' social, emotional, and moral competencies and their teaching of social, emotional, and moral competencies: The mediating role of perceived importance and teaching planning</t>
-  </si>
-  <si>
-    <t>This longitudinal study examined the association between teachers' Social, Emotional, and Moral Competencies (SEMC) and their teaching of SEMC, considering the mediating effect of perception of the importance of promoting SEMC and planning of the teaching of SEMC. The sample included 731 teachers at Wave 1 and 1131 teachers at Wave 2, with 370 teachers participating in both waves. Results showed that teachers' SEMC positively predicted their teaching of SEMC, mediated by perception of the importance of promoting SEMC and planning of the teaching of SEMC. Findings suggest the need to develop specific teacher training to promote these competencies among students.</t>
-  </si>
-  <si>
-    <t>include</t>
-  </si>
-  <si>
-    <t>rayyan-409799137</t>
-  </si>
-  <si>
-    <t>10.1016/j.lindif.2025.102844</t>
-  </si>
-  <si>
-    <t>LEARNING AND INDIVIDUAL DIFFERENCES</t>
-  </si>
-  <si>
-    <t>Guo, Jiesi and Greiff, Samuel and Tang, Xin</t>
-  </si>
-  <si>
-    <t>Shaping the socio-emotional landscape: Advances, mechanisms, and contexts in learning and individual differences</t>
-  </si>
-  <si>
-    <t>rayyan-409799147</t>
-  </si>
-  <si>
-    <t>10.3390/su172310580</t>
-  </si>
-  <si>
-    <t>Sustainability (Switzerland)</t>
-  </si>
-  <si>
-    <t>Yao, Zhuojun and Li, Meishi and Liu, Hanyao</t>
-  </si>
-  <si>
-    <t>Cultivating Care Through Nature: A Meta-Analysis of Nature Connectedness and Prosociality</t>
-  </si>
-  <si>
-    <t>rayyan-409799148</t>
-  </si>
-  <si>
-    <t>10.11591/ijere.v14i6.35535</t>
-  </si>
-  <si>
-    <t>International Journal of Evaluation and Research in Education</t>
-  </si>
-  <si>
-    <t>Thiamta, Pantipa and Damrongpanit, Suntonrapot</t>
-  </si>
-  <si>
-    <t>From family to classroom: mediating roles in promoting social and emotional learning among early adolescents</t>
-  </si>
-  <si>
-    <t>rayyan-409799149</t>
-  </si>
-  <si>
-    <t>10.3390/educsci15111518</t>
-  </si>
-  <si>
-    <t>Education Sciences</t>
-  </si>
-  <si>
-    <t>Liu, Ji and Tahri, Dahman and Aziku, Millicent and Mbowe, Airini</t>
-  </si>
-  <si>
-    <t>Student-Driven Instruction, Agency, and Curiosity: Mediation Evidence from 46,084 Subjects Across Multiple Sites</t>
-  </si>
-  <si>
-    <t>rayyan-409799150</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2025.1673500</t>
-  </si>
-  <si>
-    <t>Frontiers in Education</t>
-  </si>
-  <si>
-    <t>Sparks, Jesse R. and Lehman, Blair A. and Gladstone, Jessica R. and Zhang, Shan and Schroeder, Noah Lee and Israel, Maya</t>
-  </si>
-  <si>
-    <t>Measuring persistence and academic resilience of Kâˆ’12 students: systematic review and operational definitions</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,25 +59,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -252,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -286,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -321,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,200 +350,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="7" max="7" width="182.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rayyan-409799136</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10.1016/j.tate.2025.105340</t>
+        </is>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TEACHING AND TEACHER EDUCATION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yuste-Hidalgo, Francisco and Stefanelli, Federica and Menesini, Ersilia and Llorent, Vicente J.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Longitudinal association between teachers' social, emotional, and moral competencies and their teaching of social, emotional, and moral competencies: The mediating role of perceived importance and teaching planning</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>This longitudinal study examined the association between teachers' Social, Emotional, and Moral Competencies (SEMC) and their teaching of SEMC, considering the mediating effect of perception of the importance of promoting SEMC and planning of the teaching of SEMC. The sample included 731 teachers at Wave 1 and 1131 teachers at Wave 2, with 370 teachers participating in both waves. Results showed that teachers' SEMC positively predicted their teaching of SEMC, mediated by perception of the importance of promoting SEMC and planning of the teaching of SEMC. Findings suggest the need to develop specific teacher training to promote these competencies among students.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rayyan-409799137</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.1016/j.lindif.2025.102844</t>
+        </is>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LEARNING AND INDIVIDUAL DIFFERENCES</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guo, Jiesi and Greiff, Samuel and Tang, Xin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Shaping the socio-emotional landscape: Advances, mechanisms, and contexts in learning and individual differences</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rayyan-409799147</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10.3390/su172310580</t>
+        </is>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sustainability (Switzerland)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yao, Zhuojun and Li, Meishi and Liu, Hanyao</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cultivating Care Through Nature: A Meta-Analysis of Nature Connectedness and Prosociality</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rayyan-409799148</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.11591/ijere.v14i6.35535</t>
+        </is>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>International Journal of Evaluation and Research in Education</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thiamta, Pantipa and Damrongpanit, Suntonrapot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>From family to classroom: mediating roles in promoting social and emotional learning among early adolescents</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rayyan-409799149</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.3390/educsci15111518</t>
+        </is>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Education Sciences</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Liu, Ji and Tahri, Dahman and Aziku, Millicent and Mbowe, Airini</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Student-Driven Instruction, Agency, and Curiosity: Mediation Evidence from 46,084 Subjects Across Multiple Sites</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rayyan-409799150</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.3389/feduc.2025.1673500</t>
+        </is>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Frontiers in Education</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sparks, Jesse R. and Lehman, Blair A. and Gladstone, Jessica R. and Zhang, Shan and Schroeder, Noah Lee and Israel, Maya</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Measuring persistence and academic resilience of Kâˆ’12 students: systematic review and operational definitions</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
   </sheetData>
